--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AD4EDFF-E0CC-466D-BF85-7E20A965F0CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDED8C7-F43F-4ADB-9CEE-68BDD66F8658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8595" yWindow="-14055" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8430" yWindow="-14640" windowWidth="15525" windowHeight="13425" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
     <sheet name="Character" sheetId="2" r:id="rId2"/>
     <sheet name="Item" sheetId="3" r:id="rId3"/>
     <sheet name="Log" sheetId="4" r:id="rId4"/>
+    <sheet name="Action" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -94,6 +95,13 @@
   </si>
   <si>
     <t>{0}%</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1466,4 +1474,244 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F725632D-D667-4EF9-A0F2-E7FFA570ED70}">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>4000</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDED8C7-F43F-4ADB-9CEE-68BDD66F8658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57596A4C-4B8B-4CB9-897A-765B25BF9F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8430" yWindow="-14640" windowWidth="15525" windowHeight="13425" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="135" yWindow="-15780" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="12">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -101,6 +101,13 @@
     <t>攻撃</t>
     <rPh sb="0" eb="2">
       <t>コウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}に{1}ダメージを与えた</t>
+    <rPh sb="12" eb="13">
+      <t>アタ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1244,7 +1251,7 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1268,90 +1275,116 @@
       <c r="A2" s="2">
         <v>3000</v>
       </c>
-      <c r="B2" s="2"/>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2"/>
+      <c r="A3" s="2">
+        <v>3001</v>
+      </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
+      <c r="A4" s="2">
+        <v>3002</v>
+      </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
+      <c r="A5" s="2">
+        <v>3003</v>
+      </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
+      <c r="A6" s="2">
+        <v>3004</v>
+      </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
+      <c r="A7" s="2">
+        <v>3005</v>
+      </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
+      <c r="A8" s="2">
+        <v>3006</v>
+      </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>3007</v>
+      </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>3008</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>3009</v>
+      </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
+      <c r="A12" s="2">
+        <v>3010</v>
+      </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
+      <c r="A13" s="2">
+        <v>3011</v>
+      </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>3012</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57596A4C-4B8B-4CB9-897A-765B25BF9F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F9AB82-F60F-4539-A142-81A7FC7D47FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="135" yWindow="-15780" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1785" yWindow="-15405" windowWidth="15525" windowHeight="13425" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -52,13 +52,6 @@
   </si>
   <si>
     <t>{0}F</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アイテム名</t>
-    <rPh sb="4" eb="5">
-      <t>メイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -108,6 +101,163 @@
     <t>{0}に{1}ダメージを与えた</t>
     <rPh sb="12" eb="13">
       <t>アタ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ポーション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食べ物1</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食べ物5</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>食べ物6</t>
+    <rPh sb="0" eb="1">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖1</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖2</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖3</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖4</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖5</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖6</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖7</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖8</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>杖9</t>
+    <rPh sb="0" eb="1">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>巻物</t>
+    <rPh sb="0" eb="2">
+      <t>マキモノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬1</t>
+    <rPh sb="0" eb="1">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>薬2</t>
+    <rPh sb="0" eb="1">
+      <t>クスリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>焼けた食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>黒こげの食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クロ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐った食べ物</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>タ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>モノ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -497,7 +647,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -508,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -734,7 +884,7 @@
         <v>1000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -745,7 +895,7 @@
         <v>1001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -756,7 +906,7 @@
         <v>1002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -767,7 +917,7 @@
         <v>1003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1011,7 +1161,7 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1036,134 +1186,206 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="A3" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="2">
+        <v>2002</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="A5" s="2">
+        <v>2100</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>2101</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="2">
+        <v>2102</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="2">
+        <v>2103</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="A9" s="2">
+        <v>2104</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>13</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="A10" s="2">
+        <v>2105</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="A11" s="2">
+        <v>2200</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>15</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="2">
+        <v>2201</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="2">
+        <v>2202</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="A14" s="2">
+        <v>2203</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="A15" s="2">
+        <v>2204</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="2">
+        <v>2205</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2"/>
+      <c r="A17" s="2">
+        <v>2206</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="A18" s="2">
+        <v>2207</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="A19" s="2">
+        <v>2208</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="A20" s="2">
+        <v>2300</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
@@ -1276,7 +1498,7 @@
         <v>3000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1540,7 +1762,7 @@
         <v>4000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F9AB82-F60F-4539-A142-81A7FC7D47FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C666F9D9-DF0E-43DD-9DC4-702C8330AC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="-15405" windowWidth="15525" windowHeight="13425" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="510" yWindow="-14880" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -258,6 +258,23 @@
     </rPh>
     <rPh sb="5" eb="6">
       <t>モノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}を拾った</t>
+    <rPh sb="4" eb="5">
+      <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムが一杯で{0}を拾えなかった</t>
+    <rPh sb="5" eb="7">
+      <t>イッパイ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒロ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1473,7 +1490,7 @@
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1508,7 +1525,9 @@
       <c r="A3" s="2">
         <v>3001</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1517,7 +1536,9 @@
       <c r="A4" s="2">
         <v>3002</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C666F9D9-DF0E-43DD-9DC4-702C8330AC33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DA5DD8-B0A3-4A35-BA62-FE2A92852121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="510" yWindow="-14880" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9720" yWindow="-13470" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -275,6 +275,48 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>ヒロ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>使う</t>
+    <rPh sb="0" eb="1">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>置く</t>
+    <rPh sb="0" eb="1">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>装備</t>
+    <rPh sb="0" eb="2">
+      <t>ソウビ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>外す</t>
+    <rPh sb="0" eb="1">
+      <t>ハズ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アイテムを置けなかった</t>
+    <rPh sb="5" eb="6">
+      <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}を置いた</t>
+    <rPh sb="4" eb="5">
+      <t>オ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -682,49 +724,71 @@
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="A5" s="2">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>21</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
+      <c r="A7" s="2">
+        <v>22</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="A8" s="2">
+        <v>23</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>35</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
+      <c r="A9" s="2">
+        <v>24</v>
+      </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
+      <c r="A10" s="2">
+        <v>25</v>
+      </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="2"/>
+      <c r="A11" s="2">
+        <v>26</v>
+      </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1547,7 +1611,9 @@
       <c r="A5" s="2">
         <v>3003</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -1556,7 +1622,9 @@
       <c r="A6" s="2">
         <v>3004</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DA5DD8-B0A3-4A35-BA62-FE2A92852121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF9230-AF19-4875-BA0F-2CCD12F8BC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="-13470" windowWidth="15525" windowHeight="13425" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -317,6 +317,34 @@
     <t>{0}を置いた</t>
     <rPh sb="4" eb="5">
       <t>オ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}を使った</t>
+    <rPh sb="4" eb="5">
+      <t>ツカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}[{1}]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}のHPが{1}回復した</t>
+    <rPh sb="10" eb="12">
+      <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の満腹度が{1}回復した</t>
+    <rPh sb="4" eb="7">
+      <t>マンプクド</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>カイフク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1238,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B218483-C382-4685-8520-657DFFDA1EAB}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
@@ -1462,18 +1490,22 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="2">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="A21" s="2">
+        <v>2300</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
@@ -1540,6 +1572,13 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1633,7 +1672,9 @@
       <c r="A7" s="2">
         <v>3005</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1642,7 +1683,9 @@
       <c r="A8" s="2">
         <v>3006</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
@@ -1651,7 +1694,9 @@
       <c r="A9" s="2">
         <v>3007</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64EF9230-AF19-4875-BA0F-2CCD12F8BC4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BEF386-FD7F-4763-96AD-2503FEF7CE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12720" yWindow="-14505" windowWidth="15525" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -202,13 +202,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>巻物</t>
-    <rPh sb="0" eb="2">
-      <t>マキモノ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>薬1</t>
     <rPh sb="0" eb="1">
       <t>クスリ</t>
@@ -345,6 +338,43 @@
     </rPh>
     <rPh sb="11" eb="13">
       <t>カイフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>部屋31ダメ巻物</t>
+    <rPh sb="0" eb="2">
+      <t>ヘヤ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>マキモノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>範囲50ダメ</t>
+    <rPh sb="0" eb="2">
+      <t>ハンイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都会敵1</t>
+    <rPh sb="0" eb="2">
+      <t>トカイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>都会敵2</t>
+    <rPh sb="0" eb="2">
+      <t>トカイ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>テキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -756,7 +786,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -767,7 +797,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -778,7 +808,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -789,7 +819,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1036,7 +1066,9 @@
       <c r="A6" s="2">
         <v>1004</v>
       </c>
-      <c r="B6" s="2"/>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
@@ -1045,7 +1077,9 @@
       <c r="A7" s="2">
         <v>1005</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
@@ -1295,7 +1329,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1306,7 +1340,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1339,7 +1373,7 @@
         <v>2101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1350,7 +1384,7 @@
         <v>2102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1361,7 +1395,7 @@
         <v>2103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1493,7 +1527,7 @@
         <v>2299</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1504,15 +1538,19 @@
         <v>2300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
+      <c r="A22" s="2">
+        <v>2301</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
@@ -1629,7 +1667,7 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1640,7 +1678,7 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1651,7 +1689,7 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1662,7 +1700,7 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1673,7 +1711,7 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1684,7 +1722,7 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1695,7 +1733,7 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BEF386-FD7F-4763-96AD-2503FEF7CE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959CB5CA-5A0C-4C4F-9CFA-85DC7E95C12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12720" yWindow="-14505" windowWidth="15525" windowHeight="13425" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="-15150" windowWidth="21915" windowHeight="13425" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -375,6 +375,38 @@
     </rPh>
     <rPh sb="2" eb="3">
       <t>テキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}は焼けて{1}になってしまった</t>
+    <rPh sb="4" eb="5">
+      <t>ヤ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}は腐って{1}になってしまった</t>
+    <rPh sb="4" eb="5">
+      <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>炎攻撃</t>
+    <rPh sb="0" eb="3">
+      <t>ホノオコウゲキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}の{1}</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>腐らせる</t>
+    <rPh sb="0" eb="1">
+      <t>クサ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1743,7 +1775,9 @@
       <c r="A10" s="2">
         <v>3008</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -1752,7 +1786,9 @@
       <c r="A11" s="2">
         <v>3009</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
@@ -1761,7 +1797,9 @@
       <c r="A12" s="2">
         <v>3010</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1941,15 +1979,23 @@
       <c r="E2" s="2"/>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="A3" s="2">
+        <v>4001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="2">
+        <v>4002</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959CB5CA-5A0C-4C4F-9CFA-85DC7E95C12A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40D2D3D-535E-4D1D-A54D-78E371BC16FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="-15150" windowWidth="21915" windowHeight="13425" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10155" yWindow="-13935" windowWidth="12390" windowHeight="14055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -139,34 +139,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>杖1</t>
-    <rPh sb="0" eb="1">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杖2</t>
-    <rPh sb="0" eb="1">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杖3</t>
-    <rPh sb="0" eb="1">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>杖4</t>
-    <rPh sb="0" eb="1">
-      <t>ツエ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>杖5</t>
     <rPh sb="0" eb="1">
       <t>ツエ</t>
@@ -407,6 +379,46 @@
     <t>腐らせる</t>
     <rPh sb="0" eb="1">
       <t>クサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>場所替えの杖</t>
+    <rPh sb="0" eb="2">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>ガエノツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>雷の杖</t>
+    <rPh sb="0" eb="1">
+      <t>イカヅチ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープの杖</t>
+    <rPh sb="4" eb="5">
+      <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹き飛ばしの杖</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ツエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -818,7 +830,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -829,7 +841,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -840,7 +852,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -851,7 +863,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1099,7 +1111,7 @@
         <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1110,7 +1122,7 @@
         <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1361,7 +1373,7 @@
         <v>2000</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1372,7 +1384,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1405,7 +1417,7 @@
         <v>2101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1416,7 +1428,7 @@
         <v>2102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1427,7 +1439,7 @@
         <v>2103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1460,7 +1472,7 @@
         <v>2200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1471,7 +1483,7 @@
         <v>2201</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1482,7 +1494,7 @@
         <v>2202</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1493,7 +1505,7 @@
         <v>2203</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1504,7 +1516,7 @@
         <v>2204</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
@@ -1515,7 +1527,7 @@
         <v>2205</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
@@ -1526,7 +1538,7 @@
         <v>2206</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1537,7 +1549,7 @@
         <v>2207</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
@@ -1548,7 +1560,7 @@
         <v>2208</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
@@ -1559,7 +1571,7 @@
         <v>2299</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1570,7 +1582,7 @@
         <v>2300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1581,7 +1593,7 @@
         <v>2301</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1699,7 +1711,7 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1710,7 +1722,7 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1721,7 +1733,7 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1732,7 +1744,7 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1743,7 +1755,7 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1754,7 +1766,7 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1765,7 +1777,7 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1776,7 +1788,7 @@
         <v>3008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1787,7 +1799,7 @@
         <v>3009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1798,7 +1810,7 @@
         <v>3010</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1983,7 +1995,7 @@
         <v>4001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1994,7 +2006,7 @@
         <v>4002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B40D2D3D-535E-4D1D-A54D-78E371BC16FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478AE1DB-9F55-4B9F-AAB6-B0E092C1ED87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10155" yWindow="-13935" windowWidth="12390" windowHeight="14055" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14085" yWindow="-14265" windowWidth="12750" windowHeight="12015" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Item" sheetId="3" r:id="rId3"/>
     <sheet name="Log" sheetId="4" r:id="rId4"/>
     <sheet name="Action" sheetId="6" r:id="rId5"/>
+    <sheet name="Trap" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -181,13 +182,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>薬2</t>
-    <rPh sb="0" eb="1">
-      <t>クスリ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>焼けた食べ物</t>
     <rPh sb="0" eb="1">
       <t>ヤ</t>
@@ -419,6 +413,54 @@
     </rPh>
     <rPh sb="6" eb="7">
       <t>ツエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}を踏んだ</t>
+    <rPh sb="4" eb="5">
+      <t>フ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}は発動しなかった</t>
+    <rPh sb="4" eb="6">
+      <t>ハツドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ダメージの罠</t>
+    <rPh sb="5" eb="6">
+      <t>ワナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>吹き飛ばしの罠</t>
+    <rPh sb="0" eb="1">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ト</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ワナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワープの罠</t>
+    <rPh sb="4" eb="5">
+      <t>ワナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目薬</t>
+    <rPh sb="0" eb="2">
+      <t>メグスリ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -830,7 +872,7 @@
         <v>20</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -841,7 +883,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -852,7 +894,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -863,7 +905,7 @@
         <v>23</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1111,7 +1153,7 @@
         <v>1004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1122,7 +1164,7 @@
         <v>1005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1384,7 +1426,7 @@
         <v>2001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1417,7 +1459,7 @@
         <v>2101</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1428,7 +1470,7 @@
         <v>2102</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1439,7 +1481,7 @@
         <v>2103</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1472,7 +1514,7 @@
         <v>2200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1483,7 +1525,7 @@
         <v>2201</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1494,7 +1536,7 @@
         <v>2202</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -1505,7 +1547,7 @@
         <v>2203</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
@@ -1571,7 +1613,7 @@
         <v>2299</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
@@ -1582,7 +1624,7 @@
         <v>2300</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -1593,7 +1635,7 @@
         <v>2301</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -1711,7 +1753,7 @@
         <v>3001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1722,7 +1764,7 @@
         <v>3002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -1733,7 +1775,7 @@
         <v>3003</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -1744,7 +1786,7 @@
         <v>3004</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1755,7 +1797,7 @@
         <v>3005</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1766,7 +1808,7 @@
         <v>3006</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
@@ -1777,7 +1819,7 @@
         <v>3007</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
@@ -1788,7 +1830,7 @@
         <v>3008</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
@@ -1799,7 +1841,7 @@
         <v>3009</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
@@ -1810,7 +1852,7 @@
         <v>3010</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
@@ -1820,7 +1862,9 @@
       <c r="A13" s="2">
         <v>3011</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1829,27 +1873,35 @@
       <c r="A14" s="2">
         <v>3012</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>3013</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
+      <c r="A16" s="2">
+        <v>3014</v>
+      </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2">
+        <v>3015</v>
+      </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
@@ -1995,7 +2047,7 @@
         <v>4001</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -2006,7 +2058,7 @@
         <v>4002</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
@@ -2199,4 +2251,252 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7457124-E634-4C33-B1B4-772DC2F94819}">
+  <dimension ref="A1:E30"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
+  <cols>
+    <col min="1" max="1" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2">
+        <v>5001</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2">
+        <v>5002</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{478AE1DB-9F55-4B9F-AAB6-B0E092C1ED87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0473B2-3C12-49B9-A7AE-B04668432D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14085" yWindow="-14265" windowWidth="12750" windowHeight="12015" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15435" yWindow="-13980" windowWidth="12750" windowHeight="12015" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -461,6 +461,20 @@
     <t>目薬</t>
     <rPh sb="0" eb="2">
       <t>メグスリ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>地雷</t>
+    <rPh sb="0" eb="2">
+      <t>ジライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大型地雷</t>
+    <rPh sb="0" eb="4">
+      <t>オオガタジライ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -2313,15 +2327,23 @@
       <c r="E4" s="2"/>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="A5" s="2">
+        <v>5003</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="A6" s="2">
+        <v>5004</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>

--- a/Assets/Resources/MasterData/MessageData.xlsx
+++ b/Assets/Resources/MasterData/MessageData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0473B2-3C12-49B9-A7AE-B04668432D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C421EEF-43B2-4A3F-9DB6-3EBFC48F1944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15435" yWindow="-13980" windowWidth="12750" windowHeight="12015" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Menu" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="62">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -475,6 +475,41 @@
     <t>大型地雷</t>
     <rPh sb="0" eb="4">
       <t>オオガタジライ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>いいえ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>次の階に進みますか？</t>
+    <rPh sb="0" eb="1">
+      <t>ツギ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スス</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>投げる</t>
+    <rPh sb="0" eb="1">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>{0}を投げた</t>
+    <rPh sb="4" eb="5">
+      <t>ナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -824,11 +859,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -883,10 +918,10 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>26</v>
+        <v>57</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
@@ -894,10 +929,10 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="2">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -905,84 +940,102 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2">
-        <v>22</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>28</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2">
-        <v>23</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2">
-        <v>24</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2">
-        <v>25</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="2">
-        <v>26</v>
-      </c>
-      <c r="B11" s="2"/>
+        <v>22</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
+      <c r="A12" s="2">
+        <v>23</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="A13" s="2">
+        <v>24</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="2"/>
+      <c r="A14" s="2">
+        <v>25</v>
+      </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="2"/>
+      <c r="A15" s="2">
+        <v>26</v>
+      </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="A16" s="2">
+        <v>30</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>59</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1084,6 +1137,34 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1898,7 +1979,9 @@
       <c r="A15" s="2">
         <v>3013</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
